--- a/app/data/Live_Metrics.xlsx
+++ b/app/data/Live_Metrics.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ionization flame sensor current signal.</t>
+          <t>Ionisation flame sensor current signal.</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Primary central heating loop flow velocity.</t>
+          <t>Primary heating-loop flow velocity.</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Appliance flow header temperature.</t>
+          <t>Appliance flow-header temperature.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Substation telemetry warnings active in Sector 4.</t>
+          <t>Active substation telemetry warnings in sector 4.</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Active unplanned outage count across network.</t>
+          <t>Active unplanned outages across the network.</t>
         </is>
       </c>
     </row>
